--- a/Proyecto/Fase2/techcore-odoo/3_Proveedores_Odoo.xlsx
+++ b/Proyecto/Fase2/techcore-odoo/3_Proveedores_Odoo.xlsx
@@ -417,38 +417,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>company_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>supplier_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -457,23 +463,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>techcore_prov_ingram_micro_guatemala</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Ingram Micro Guatemala</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>ventas@ingrammicro.com.gt</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Productos: Procesadores, RAM, SSD, Tarjetas Madre. Condiciones de pago: 30 días crédito</t>
         </is>
@@ -482,23 +493,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>techcore_prov_intcomex</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Intcomex</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>info@intcomex.com.gt</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Productos: Switches, Servidores, Redes. Condiciones de pago: 15 días crédito</t>
         </is>
@@ -507,23 +523,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>techcore_prov_pc_mayorista</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>PC Mayorista</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>contacto@pcmayorista.gt</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Productos: Componentes generales. Condiciones de pago: Contado</t>
         </is>
